--- a/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/larher_chalmers_se/Documents/Documents/GitHub/oa-tskr/Bibsam_tidskriftslistor/Uppdateringar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{6196CB09-7FD6-4A1E-892B-3CCDA4F90521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA5C0043-CDA9-404C-91D1-3339AEA492E9}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{6196CB09-7FD6-4A1E-892B-3CCDA4F90521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{790B61B2-ACC9-4DE1-83A8-792D3FA54EA9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan8" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Nr4_feb19" sheetId="5" r:id="rId5"/>
     <sheet name="Nr5_feb24" sheetId="6" r:id="rId6"/>
     <sheet name="Nr6_mars06" sheetId="7" r:id="rId7"/>
+    <sheet name="Nr7_mars19" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5378" uniqueCount="2478">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5915" uniqueCount="2699">
   <si>
     <t>Imprint</t>
   </si>
@@ -7476,6 +7477,669 @@
   </si>
   <si>
     <t>https://www.mdpi.com/journal/wild</t>
+  </si>
+  <si>
+    <t>2071-1409</t>
+  </si>
+  <si>
+    <t>1680-8584</t>
+  </si>
+  <si>
+    <t>Aerosol and Air Quality Research</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/journal/44408</t>
+  </si>
+  <si>
+    <t>SPIE</t>
+  </si>
+  <si>
+    <t>3005-4745</t>
+  </si>
+  <si>
+    <t>Biophotonics Discovery</t>
+  </si>
+  <si>
+    <t>https://www.spiedigitallibrary.org/journals/biophotonics-discovery</t>
+  </si>
+  <si>
+    <t>2791-1748</t>
+  </si>
+  <si>
+    <t>Photonics Insights</t>
+  </si>
+  <si>
+    <t>https://www.spiedigitallibrary.org/journals/photonics-insights</t>
+  </si>
+  <si>
+    <t>2169-4834</t>
+  </si>
+  <si>
+    <t>2169-4826</t>
+  </si>
+  <si>
+    <t>Clinical Practice in Pediatric Psychology</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/PPX</t>
+  </si>
+  <si>
+    <t>1943-3280</t>
+  </si>
+  <si>
+    <t>0036-8237</t>
+  </si>
+  <si>
+    <t>Science &amp; Society</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/SSO</t>
+  </si>
+  <si>
+    <t>2701-8466</t>
+  </si>
+  <si>
+    <t>2701-9276</t>
+  </si>
+  <si>
+    <t>Journal of Cultural Management and Cultural Policy</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/CUP</t>
+  </si>
+  <si>
+    <t>3050-5461</t>
+  </si>
+  <si>
+    <t>Accounting Open</t>
+  </si>
+  <si>
+    <t>1000-6818</t>
+  </si>
+  <si>
+    <t>Acta Physico-Chimica Sinica</t>
+  </si>
+  <si>
+    <t>2773-045X</t>
+  </si>
+  <si>
+    <t>Advanced Sensor and Energy Materials</t>
+  </si>
+  <si>
+    <t>3050-6964</t>
+  </si>
+  <si>
+    <t>Advances in Patient-Reported Outcomes</t>
+  </si>
+  <si>
+    <t>0570-1783</t>
+  </si>
+  <si>
+    <t>Annals of Agricultural Sciences</t>
+  </si>
+  <si>
+    <t>0003-4967</t>
+  </si>
+  <si>
+    <t>3050-5674</t>
+  </si>
+  <si>
+    <t>ASPET Discovery</t>
+  </si>
+  <si>
+    <t>2693-1257</t>
+  </si>
+  <si>
+    <t>BioDesign Research</t>
+  </si>
+  <si>
+    <t>3050-5917</t>
+  </si>
+  <si>
+    <t>Brain and Environment</t>
+  </si>
+  <si>
+    <t>3050-6603</t>
+  </si>
+  <si>
+    <t>Carbon Neutral Technologies</t>
+  </si>
+  <si>
+    <t>2950-6433</t>
+  </si>
+  <si>
+    <t>Digital Dentistry Journal</t>
+  </si>
+  <si>
+    <t>0090-9556</t>
+  </si>
+  <si>
+    <t>Drug Metabolism and Disposition</t>
+  </si>
+  <si>
+    <t>3050-7081</t>
+  </si>
+  <si>
+    <t>EULAR Rheumatology Open</t>
+  </si>
+  <si>
+    <t>3050-7006</t>
+  </si>
+  <si>
+    <t>Finance Research Open</t>
+  </si>
+  <si>
+    <t>3050-7138</t>
+  </si>
+  <si>
+    <t>Geopsychiatry</t>
+  </si>
+  <si>
+    <t>3050-7871</t>
+  </si>
+  <si>
+    <t>In Silico Research in Biomedicine</t>
+  </si>
+  <si>
+    <t>2772-431X</t>
+  </si>
+  <si>
+    <t>Infectious Medicine</t>
+  </si>
+  <si>
+    <t>2214-3173</t>
+  </si>
+  <si>
+    <t>Information Processing in Agriculture</t>
+  </si>
+  <si>
+    <t>1048-891X</t>
+  </si>
+  <si>
+    <t>JACEP Open</t>
+  </si>
+  <si>
+    <t>2307-1877</t>
+  </si>
+  <si>
+    <t>Journal of Engineering Research</t>
+  </si>
+  <si>
+    <t>2324-2426</t>
+  </si>
+  <si>
+    <t>Journal of Neurorestoratology</t>
+  </si>
+  <si>
+    <t>3050-7901</t>
+  </si>
+  <si>
+    <t>Journal of Strategy &amp; Innovation</t>
+  </si>
+  <si>
+    <t>3050-6441</t>
+  </si>
+  <si>
+    <t>Measurement: Digitalization</t>
+  </si>
+  <si>
+    <t>0026-895X</t>
+  </si>
+  <si>
+    <t>Molecular Pharmacology</t>
+  </si>
+  <si>
+    <t>3050-6204</t>
+  </si>
+  <si>
+    <t>NAM Journal</t>
+  </si>
+  <si>
+    <t>3050-7235</t>
+  </si>
+  <si>
+    <t>Next Bioengineering</t>
+  </si>
+  <si>
+    <t>3050-7243</t>
+  </si>
+  <si>
+    <t>Next Chemical Engineering</t>
+  </si>
+  <si>
+    <t>3050-7847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Research, Data Analytics and Logistics </t>
+  </si>
+  <si>
+    <t>0031-6997</t>
+  </si>
+  <si>
+    <t>Pharmacological Reviews</t>
+  </si>
+  <si>
+    <t>2643-6515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant Phenomics </t>
+  </si>
+  <si>
+    <t>2950-4848</t>
+  </si>
+  <si>
+    <t>Psychedelics</t>
+  </si>
+  <si>
+    <t>3050-6565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research in Autism </t>
+  </si>
+  <si>
+    <t>2772-8307</t>
+  </si>
+  <si>
+    <t>Superconductivity</t>
+  </si>
+  <si>
+    <t>2534-773X</t>
+  </si>
+  <si>
+    <t>The Journal of Aging Research &amp; Lifestyle</t>
+  </si>
+  <si>
+    <t>3050-6247</t>
+  </si>
+  <si>
+    <t>The Journal of Nutritional Physiology</t>
+  </si>
+  <si>
+    <t>0022-3565</t>
+  </si>
+  <si>
+    <t>The Journal of Pharmacology and Experimental Therapeutics</t>
+  </si>
+  <si>
+    <t>3050-6328</t>
+  </si>
+  <si>
+    <t>The Journal of Precision Medicine: Health and Disease</t>
+  </si>
+  <si>
+    <t>3050-6417</t>
+  </si>
+  <si>
+    <t>Total Environment Microbiology</t>
+  </si>
+  <si>
+    <t>3050-6972</t>
+  </si>
+  <si>
+    <t>Urban Transitions</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30505461</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/10006818</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/2773045X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506964</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/05701783</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/00034967</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30505674</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/26931257</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30505917</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506603</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/29506433</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/00909556</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507081</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507006</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507138</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507871</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/2772431X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/22143173</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/1048891X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/10416102</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/26881152</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/23071877</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/23242426</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507901</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506441</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/0026895X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506204</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507235</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507243</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30507847</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/00316997</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/26436515</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/29504848</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506565</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/27728307</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/2534773X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506247</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/00223565</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506328</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506417</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506972</t>
+  </si>
+  <si>
+    <t>Cell Press</t>
+  </si>
+  <si>
+    <t>3050-5623</t>
+  </si>
+  <si>
+    <t>Cell Biomaterials</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30505623</t>
+  </si>
+  <si>
+    <t>1887-8369</t>
+  </si>
+  <si>
+    <t>Revista Internacional de Acupuntura</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/18878369</t>
+  </si>
+  <si>
+    <t>1047-8310</t>
+  </si>
+  <si>
+    <t>The Journal of High Technology Management Research</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/10478310</t>
+  </si>
+  <si>
+    <t>2214-7853</t>
+  </si>
+  <si>
+    <t>Materials Today: Proceedings</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/22147853</t>
+  </si>
+  <si>
+    <t>2405-6014</t>
+  </si>
+  <si>
+    <t>Nuclear and Particle Physics Proceedings</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/24056014</t>
+  </si>
+  <si>
+    <t>2211-6923</t>
+  </si>
+  <si>
+    <t>Operations Research for Health Care</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/22116923</t>
+  </si>
+  <si>
+    <t>1750-9467</t>
+  </si>
+  <si>
+    <t>Research in Autism Spectrum Disorders</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/17509467</t>
+  </si>
+  <si>
+    <t>2468-4988</t>
+  </si>
+  <si>
+    <t>Journal of Immunology and Regenerative Medicine</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/24684988</t>
+  </si>
+  <si>
+    <t>0030-4387</t>
+  </si>
+  <si>
+    <t>Orbis</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/00304387</t>
+  </si>
+  <si>
+    <t>2605-0730</t>
+  </si>
+  <si>
+    <t>Atención Primaria Práctica</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/26050730</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>2666-5220</t>
+  </si>
+  <si>
+    <t>Brain Multiphysics</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/26665220</t>
+  </si>
+  <si>
+    <t>2590-1516</t>
+  </si>
+  <si>
+    <t>Contraception: X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/25901516</t>
+  </si>
+  <si>
+    <t>2590-2555</t>
+  </si>
+  <si>
+    <t>Current Research in Immunology</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/25902555</t>
+  </si>
+  <si>
+    <t>2590-2504</t>
+  </si>
+  <si>
+    <t>La Presse Médicale Open</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/25902504</t>
+  </si>
+  <si>
+    <t>1878-5352</t>
+  </si>
+  <si>
+    <t>Arabian Journal of Chemistry</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/18785352</t>
+  </si>
+  <si>
+    <t>2950-3280</t>
+  </si>
+  <si>
+    <t>Blood Neoplasia</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/29503280</t>
+  </si>
+  <si>
+    <t>2950-3272</t>
+  </si>
+  <si>
+    <t>Blood Vessels, Thrombosis &amp; Hemostasis</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/29503272</t>
+  </si>
+  <si>
+    <t>2405-8572</t>
+  </si>
+  <si>
+    <t>International Journal of Surgery Open</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/24058572</t>
+  </si>
+  <si>
+    <t>2095-3119</t>
+  </si>
+  <si>
+    <t>Journal of Integrative Agriculture</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/20953119</t>
+  </si>
+  <si>
+    <t>Journal of King Saud University: Computer and Information Sciences</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/13191578</t>
+  </si>
+  <si>
+    <t>1018-3647</t>
+  </si>
+  <si>
+    <t>Journal of King Saud University: Science</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/10183647</t>
+  </si>
+  <si>
+    <t>1319-6103</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/13196103</t>
+  </si>
+  <si>
+    <t>2666-769X</t>
+  </si>
+  <si>
+    <t>Orthoplastic Surgery</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/2666769X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/10139052</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/13190164</t>
+  </si>
+  <si>
+    <t>2667-1093</t>
+  </si>
+  <si>
+    <t>Chem Catalysis</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/26671093</t>
+  </si>
+  <si>
+    <t>2666-9986</t>
+  </si>
+  <si>
+    <t>Device</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/26669986</t>
+  </si>
+  <si>
+    <t>2950-6360</t>
+  </si>
+  <si>
+    <t>Newton</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/29506360</t>
   </si>
 </sst>
 </file>
@@ -25649,4 +26313,1777 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70A5D19D-B83B-4C25-B766-52A3F7386D61}">
+  <dimension ref="A1:H76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2478</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2484</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2485</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2487</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2489</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2490</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2493</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2494</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2495</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2496</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>543</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2497</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2498</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2499</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2504</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2579</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2505</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2506</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2580</v>
+      </c>
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2507</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2508</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2582</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2511</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2512</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2584</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2586</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2519</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2521</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2523</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2524</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2525</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2590</v>
+      </c>
+      <c r="F20" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2527</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F21" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2529</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2592</v>
+      </c>
+      <c r="F22" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2530</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2531</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2593</v>
+      </c>
+      <c r="F23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2533</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2594</v>
+      </c>
+      <c r="F24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2595</v>
+      </c>
+      <c r="F25" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D26" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2596</v>
+      </c>
+      <c r="F26" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" t="s">
+        <v>139</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2597</v>
+      </c>
+      <c r="F27" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1586</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2598</v>
+      </c>
+      <c r="F28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D29" t="s">
+        <v>2539</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2599</v>
+      </c>
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B31" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D31" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E31" t="s">
+        <v>2601</v>
+      </c>
+      <c r="F31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B32" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E32" t="s">
+        <v>2602</v>
+      </c>
+      <c r="F32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B33" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D33" t="s">
+        <v>2547</v>
+      </c>
+      <c r="E33" t="s">
+        <v>2603</v>
+      </c>
+      <c r="F33" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2604</v>
+      </c>
+      <c r="F34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2550</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2605</v>
+      </c>
+      <c r="F35" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2552</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2606</v>
+      </c>
+      <c r="F36" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2554</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2607</v>
+      </c>
+      <c r="F37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2557</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2608</v>
+      </c>
+      <c r="F38" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2609</v>
+      </c>
+      <c r="F39" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2560</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2610</v>
+      </c>
+      <c r="F40" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B41" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2563</v>
+      </c>
+      <c r="E41" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F41" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B42" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D42" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E42" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2613</v>
+      </c>
+      <c r="F43" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2569</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2614</v>
+      </c>
+      <c r="F44" t="s">
+        <v>34</v>
+      </c>
+      <c r="G44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2615</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2616</v>
+      </c>
+      <c r="F46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2617</v>
+      </c>
+      <c r="F47" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" t="s">
+        <v>20</v>
+      </c>
+      <c r="H47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2618</v>
+      </c>
+      <c r="F48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2624</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2625</v>
+      </c>
+      <c r="F49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B50" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D50" t="s">
+        <v>2627</v>
+      </c>
+      <c r="E50" t="s">
+        <v>2628</v>
+      </c>
+      <c r="F50" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" t="s">
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D51" t="s">
+        <v>2630</v>
+      </c>
+      <c r="E51" t="s">
+        <v>2631</v>
+      </c>
+      <c r="F51" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" t="s">
+        <v>20</v>
+      </c>
+      <c r="H51" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B52" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2633</v>
+      </c>
+      <c r="E52" t="s">
+        <v>2634</v>
+      </c>
+      <c r="F52" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" t="s">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B53" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D53" t="s">
+        <v>2636</v>
+      </c>
+      <c r="E53" t="s">
+        <v>2637</v>
+      </c>
+      <c r="F53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" t="s">
+        <v>20</v>
+      </c>
+      <c r="H53" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B54" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2639</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2640</v>
+      </c>
+      <c r="F54" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B55" t="s">
+        <v>2641</v>
+      </c>
+      <c r="D55" t="s">
+        <v>2642</v>
+      </c>
+      <c r="E55" t="s">
+        <v>2643</v>
+      </c>
+      <c r="F55" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" t="s">
+        <v>20</v>
+      </c>
+      <c r="H55" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B56" t="s">
+        <v>2644</v>
+      </c>
+      <c r="D56" t="s">
+        <v>2645</v>
+      </c>
+      <c r="E56" t="s">
+        <v>2646</v>
+      </c>
+      <c r="F56" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B57" t="s">
+        <v>2647</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2648</v>
+      </c>
+      <c r="E57" t="s">
+        <v>2649</v>
+      </c>
+      <c r="F57" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G57" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D58" t="s">
+        <v>2652</v>
+      </c>
+      <c r="E58" t="s">
+        <v>2653</v>
+      </c>
+      <c r="F58" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G58" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B59" t="s">
+        <v>2654</v>
+      </c>
+      <c r="D59" t="s">
+        <v>2655</v>
+      </c>
+      <c r="E59" t="s">
+        <v>2656</v>
+      </c>
+      <c r="F59" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G59" t="s">
+        <v>20</v>
+      </c>
+      <c r="H59" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B60" t="s">
+        <v>2657</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2658</v>
+      </c>
+      <c r="E60" t="s">
+        <v>2659</v>
+      </c>
+      <c r="F60" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G60" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B61" t="s">
+        <v>2660</v>
+      </c>
+      <c r="D61" t="s">
+        <v>2661</v>
+      </c>
+      <c r="E61" t="s">
+        <v>2662</v>
+      </c>
+      <c r="F61" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G61" t="s">
+        <v>20</v>
+      </c>
+      <c r="H61" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2663</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2664</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2665</v>
+      </c>
+      <c r="F62" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G62" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2666</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2667</v>
+      </c>
+      <c r="E63" t="s">
+        <v>2668</v>
+      </c>
+      <c r="F63" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G63" t="s">
+        <v>20</v>
+      </c>
+      <c r="H63" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2669</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2670</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2671</v>
+      </c>
+      <c r="F64" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G64" t="s">
+        <v>20</v>
+      </c>
+      <c r="H64" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2672</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2673</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2674</v>
+      </c>
+      <c r="F65" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G65" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2675</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2676</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2677</v>
+      </c>
+      <c r="F66" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G66" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2678</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2679</v>
+      </c>
+      <c r="F67" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G67" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2680</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2681</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2682</v>
+      </c>
+      <c r="F68" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G68" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2683</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E69" t="s">
+        <v>2684</v>
+      </c>
+      <c r="F69" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G69" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2685</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2686</v>
+      </c>
+      <c r="E70" t="s">
+        <v>2687</v>
+      </c>
+      <c r="F70" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G70" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E71" t="s">
+        <v>2688</v>
+      </c>
+      <c r="F71" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G71" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1262</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1263</v>
+      </c>
+      <c r="E72" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F72" t="s">
+        <v>2650</v>
+      </c>
+      <c r="G72" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2690</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2691</v>
+      </c>
+      <c r="E73" t="s">
+        <v>2692</v>
+      </c>
+      <c r="F73" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2693</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2694</v>
+      </c>
+      <c r="E74" t="s">
+        <v>2695</v>
+      </c>
+      <c r="F74" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2696</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2697</v>
+      </c>
+      <c r="E75" t="s">
+        <v>2698</v>
+      </c>
+      <c r="F75" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" t="s">
+        <v>20</v>
+      </c>
+      <c r="H75" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2621</v>
+      </c>
+      <c r="E76" t="s">
+        <v>2622</v>
+      </c>
+      <c r="F76" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/larher_chalmers_se/Documents/Documents/GitHub/oa-tskr/Bibsam_tidskriftslistor/Uppdateringar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{6196CB09-7FD6-4A1E-892B-3CCDA4F90521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{790B61B2-ACC9-4DE1-83A8-792D3FA54EA9}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{6196CB09-7FD6-4A1E-892B-3CCDA4F90521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3DED18-3EA1-4440-A8FE-33AE9782538B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan8" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="Nr5_feb24" sheetId="6" r:id="rId6"/>
     <sheet name="Nr6_mars06" sheetId="7" r:id="rId7"/>
     <sheet name="Nr7_mars19" sheetId="8" r:id="rId8"/>
+    <sheet name="Nr8_april2" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5915" uniqueCount="2699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5946" uniqueCount="2711">
   <si>
     <t>Imprint</t>
   </si>
@@ -8140,6 +8141,42 @@
   </si>
   <si>
     <t>http://www.sciencedirect.com/science/journal/29506360</t>
+  </si>
+  <si>
+    <t>1653-1868 </t>
+  </si>
+  <si>
+    <t>2004-5190</t>
+  </si>
+  <si>
+    <t>Educare</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/educare</t>
+  </si>
+  <si>
+    <t>CC BY-NC</t>
+  </si>
+  <si>
+    <t>1368-1613</t>
+  </si>
+  <si>
+    <t>Information Research</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/ir</t>
+  </si>
+  <si>
+    <t>2001-3345</t>
+  </si>
+  <si>
+    <t>1401-6788</t>
+  </si>
+  <si>
+    <t>Pedagogisk forskning i Sverige</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/pfs</t>
   </si>
 </sst>
 </file>
@@ -28086,4 +28123,115 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BAE57A0-8F2E-449C-9190-7002125CF58A}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2699</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2700</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2701</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2702</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>2703</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2704</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2705</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2706</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>2703</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2707</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2708</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2709</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2710</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/larher_chalmers_se/Documents/Documents/GitHub/oa-tskr/Bibsam_tidskriftslistor/Uppdateringar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="8_{6196CB09-7FD6-4A1E-892B-3CCDA4F90521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3DED18-3EA1-4440-A8FE-33AE9782538B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F9646E-8B90-4E9A-8240-68274D450E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="8" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan8" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Nr6_mars06" sheetId="7" r:id="rId7"/>
     <sheet name="Nr7_mars19" sheetId="8" r:id="rId8"/>
     <sheet name="Nr8_april2" sheetId="9" r:id="rId9"/>
+    <sheet name="Nr9_april29" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5946" uniqueCount="2711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6319" uniqueCount="2827">
   <si>
     <t>Imprint</t>
   </si>
@@ -8177,6 +8178,354 @@
   </si>
   <si>
     <t>https://publicera.kb.se/pfs</t>
+  </si>
+  <si>
+    <t>3059-3883</t>
+  </si>
+  <si>
+    <t>AI, Brain and Child</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/journal/44436</t>
+  </si>
+  <si>
+    <t>3059-2003</t>
+  </si>
+  <si>
+    <t>CVIR Oncology</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/journal/44343</t>
+  </si>
+  <si>
+    <t>2833-0501</t>
+  </si>
+  <si>
+    <t>All Life Methods</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=talm</t>
+  </si>
+  <si>
+    <t>2642-0228</t>
+  </si>
+  <si>
+    <t>Lagt till e-issn</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=rica</t>
+  </si>
+  <si>
+    <t>1918-1817</t>
+  </si>
+  <si>
+    <t>0701-1784</t>
+  </si>
+  <si>
+    <t>Canadian Water Resources Journal / Revue canadienne des ressources hydriques</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=tcwr</t>
+  </si>
+  <si>
+    <t>1867-2280</t>
+  </si>
+  <si>
+    <t>0933-2480</t>
+  </si>
+  <si>
+    <t>CHANCE</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=ucha</t>
+  </si>
+  <si>
+    <t>1464-0600</t>
+  </si>
+  <si>
+    <t>0269-9931</t>
+  </si>
+  <si>
+    <t>Cognition and Emotion</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=pcem</t>
+  </si>
+  <si>
+    <t>2993-2106</t>
+  </si>
+  <si>
+    <t>Critical Insights in Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tagr</t>
+  </si>
+  <si>
+    <t>2993-2203</t>
+  </si>
+  <si>
+    <t>Critical Insights in Biophysics</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tbip</t>
+  </si>
+  <si>
+    <t>2993-2238</t>
+  </si>
+  <si>
+    <t>Critical Insights in Biotechnology</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tbte</t>
+  </si>
+  <si>
+    <t>2993-2262</t>
+  </si>
+  <si>
+    <t>Critical Insights in Microbiology</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tmic</t>
+  </si>
+  <si>
+    <t>2993-2297</t>
+  </si>
+  <si>
+    <t>Critical Insights in Plant Science</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tpls</t>
+  </si>
+  <si>
+    <t>2752-5783</t>
+  </si>
+  <si>
+    <t>Digital Twin</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tdtw</t>
+  </si>
+  <si>
+    <t>1946-7842</t>
+  </si>
+  <si>
+    <t>1529-9104</t>
+  </si>
+  <si>
+    <t>Early Medieval China</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=yemc</t>
+  </si>
+  <si>
+    <t>2997-4836</t>
+  </si>
+  <si>
+    <t>Eastern European Screen Studies</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/reec</t>
+  </si>
+  <si>
+    <t>2040-3518</t>
+  </si>
+  <si>
+    <t>2040-350X</t>
+  </si>
+  <si>
+    <t>Studies in Eastern European Cinema</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=reec</t>
+  </si>
+  <si>
+    <t>1848-9664</t>
+  </si>
+  <si>
+    <t>1331-677X</t>
+  </si>
+  <si>
+    <t>Economic Research-Ekonomska Istraživanja</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=RERO</t>
+  </si>
+  <si>
+    <t>1110-1849</t>
+  </si>
+  <si>
+    <t>Egyptian Journal of Anaesthesia</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=TEJA</t>
+  </si>
+  <si>
+    <t>1469-8307</t>
+  </si>
+  <si>
+    <t>1461-6696</t>
+  </si>
+  <si>
+    <t>European Societies</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=reus</t>
+  </si>
+  <si>
+    <t>2167-8707</t>
+  </si>
+  <si>
+    <t>Expert Opinion on Orphan Drugs</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=ieod</t>
+  </si>
+  <si>
+    <t>1834-7533</t>
+  </si>
+  <si>
+    <t>0812-3985</t>
+  </si>
+  <si>
+    <t>Exploration Geophysics</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=texg</t>
+  </si>
+  <si>
+    <t>2993-7817</t>
+  </si>
+  <si>
+    <t>Gastrointestinal Oncology: Management and Care</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/ugon</t>
+  </si>
+  <si>
+    <t>0975-007X</t>
+  </si>
+  <si>
+    <t>0019-4506</t>
+  </si>
+  <si>
+    <t>Indian Chemical Engineer</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tice</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/rjtc</t>
+  </si>
+  <si>
+    <t>1740-1909</t>
+  </si>
+  <si>
+    <t>0021-8499</t>
+  </si>
+  <si>
+    <t>Journal of Advertising Research</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/ujar</t>
+  </si>
+  <si>
+    <t>1540-8558</t>
+  </si>
+  <si>
+    <t>1050-9674</t>
+  </si>
+  <si>
+    <t>Journal of Offender Rehabilitation</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=wjor</t>
+  </si>
+  <si>
+    <t>1941-3300</t>
+  </si>
+  <si>
+    <t>0022-4561</t>
+  </si>
+  <si>
+    <t>Journal of Soil and Water Conservation</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/uswc</t>
+  </si>
+  <si>
+    <t>2997-9668</t>
+  </si>
+  <si>
+    <t>2997-965X</t>
+  </si>
+  <si>
+    <t>Justice, Opportunities, and Rehabilitation</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/wjor</t>
+  </si>
+  <si>
+    <t>3065-2669</t>
+  </si>
+  <si>
+    <t>Nano Views</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tnvs</t>
+  </si>
+  <si>
+    <t>1469-9931</t>
+  </si>
+  <si>
+    <t>0739-3148</t>
+  </si>
+  <si>
+    <t>New Political Science</t>
+  </si>
+  <si>
+    <t>http://tandfonline.com/action/journalInformation?show=aimsScope&amp;journalCode=cnps</t>
+  </si>
+  <si>
+    <t>2996-0355</t>
+  </si>
+  <si>
+    <t>Research in Biomedical Engineering and Technology</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tbci</t>
+  </si>
+  <si>
+    <t>3065-4327</t>
+  </si>
+  <si>
+    <t>Research in Materials Science</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/trms</t>
+  </si>
+  <si>
+    <t>1949-825X</t>
+  </si>
+  <si>
+    <t>1949-8241</t>
+  </si>
+  <si>
+    <t>Technology and Innovation</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/tein</t>
+  </si>
+  <si>
+    <t>1938-5447</t>
+  </si>
+  <si>
+    <t>1559-4491</t>
+  </si>
+  <si>
+    <t>The Wilson Journal of Ornithology</t>
+  </si>
+  <si>
+    <t>https://www.tandfonline.com/journals/uwjo</t>
   </si>
 </sst>
 </file>
@@ -21916,6 +22265,1233 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEDB7F21-2AC2-4C63-B0E9-3A46DC976564}">
+  <dimension ref="A1:H49"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2711</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2712</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2713</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>821</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2714</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2715</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2716</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2717</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2718</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2719</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2721</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D6" t="s">
+        <v>418</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2722</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2723</v>
+      </c>
+      <c r="C9" t="s">
+        <v>2724</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2725</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2726</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2728</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2729</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2730</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2732</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2733</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2734</v>
+      </c>
+      <c r="F12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1329</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2735</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2736</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2737</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2738</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2739</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2740</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2742</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2743</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2744</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2745</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2746</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2747</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2748</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2749</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2750</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2751</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2752</v>
+      </c>
+      <c r="F19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B20" t="s">
+        <v>2753</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2754</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2755</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2756</v>
+      </c>
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D21" t="s">
+        <v>2758</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2759</v>
+      </c>
+      <c r="F21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2760</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2761</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2762</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2763</v>
+      </c>
+      <c r="F22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2764</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2765</v>
+      </c>
+      <c r="D23" t="s">
+        <v>2766</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2767</v>
+      </c>
+      <c r="F23" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B24" t="s">
+        <v>2768</v>
+      </c>
+      <c r="D24" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2770</v>
+      </c>
+      <c r="F24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2771</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2772</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2773</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2774</v>
+      </c>
+      <c r="F25" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2775</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2776</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2777</v>
+      </c>
+      <c r="F26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B27" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2779</v>
+      </c>
+      <c r="D27" t="s">
+        <v>2780</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2781</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" t="s">
+        <v>478</v>
+      </c>
+      <c r="H27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B28" t="s">
+        <v>2782</v>
+      </c>
+      <c r="D28" t="s">
+        <v>2783</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2784</v>
+      </c>
+      <c r="F28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1357</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F29" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1361</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F30" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H30" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F31" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1367</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F32" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H32" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F33" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B34" t="s">
+        <v>2785</v>
+      </c>
+      <c r="C34" t="s">
+        <v>2786</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2787</v>
+      </c>
+      <c r="E34" t="s">
+        <v>2788</v>
+      </c>
+      <c r="F34" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H34" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B35" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C35" t="s">
+        <v>2377</v>
+      </c>
+      <c r="D35" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E35" t="s">
+        <v>2400</v>
+      </c>
+      <c r="F35" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H35" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B36" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2347</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2789</v>
+      </c>
+      <c r="F36" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H36" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C37" t="s">
+        <v>2791</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2792</v>
+      </c>
+      <c r="E37" t="s">
+        <v>2793</v>
+      </c>
+      <c r="F37" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H37" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B38" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C38" t="s">
+        <v>2795</v>
+      </c>
+      <c r="D38" t="s">
+        <v>2796</v>
+      </c>
+      <c r="E38" t="s">
+        <v>2797</v>
+      </c>
+      <c r="F38" t="s">
+        <v>26</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H38" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B39" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C39" t="s">
+        <v>2799</v>
+      </c>
+      <c r="D39" t="s">
+        <v>2800</v>
+      </c>
+      <c r="E39" t="s">
+        <v>2801</v>
+      </c>
+      <c r="F39" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H39" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B40" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C40" t="s">
+        <v>2803</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2804</v>
+      </c>
+      <c r="E40" t="s">
+        <v>2805</v>
+      </c>
+      <c r="F40" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H40" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F41" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H42" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2806</v>
+      </c>
+      <c r="D43" t="s">
+        <v>2807</v>
+      </c>
+      <c r="E43" t="s">
+        <v>2808</v>
+      </c>
+      <c r="F43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H43" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2809</v>
+      </c>
+      <c r="C44" t="s">
+        <v>2810</v>
+      </c>
+      <c r="D44" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E44" t="s">
+        <v>2812</v>
+      </c>
+      <c r="F44" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F45" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2813</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2814</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2815</v>
+      </c>
+      <c r="F46" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H46" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B47" t="s">
+        <v>2816</v>
+      </c>
+      <c r="D47" t="s">
+        <v>2817</v>
+      </c>
+      <c r="E47" t="s">
+        <v>2818</v>
+      </c>
+      <c r="F47" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H47" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B48" t="s">
+        <v>2819</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2820</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2821</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2822</v>
+      </c>
+      <c r="F48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H48" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B49" t="s">
+        <v>2823</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2824</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2825</v>
+      </c>
+      <c r="E49" t="s">
+        <v>2826</v>
+      </c>
+      <c r="F49" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1278</v>
+      </c>
+      <c r="H49" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0BCCC-3CC4-4163-A79C-06EC3FA0BA03}">
   <dimension ref="A1:H26"/>

--- a/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F9646E-8B90-4E9A-8240-68274D450E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8A57F6-CAEB-4491-843D-E6B5C0F691F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan8" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Nr7_mars19" sheetId="8" r:id="rId8"/>
     <sheet name="Nr8_april2" sheetId="9" r:id="rId9"/>
     <sheet name="Nr9_april29" sheetId="10" r:id="rId10"/>
+    <sheet name="Nr10_juni5" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6319" uniqueCount="2827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6453" uniqueCount="2881">
   <si>
     <t>Imprint</t>
   </si>
@@ -8526,6 +8527,168 @@
   </si>
   <si>
     <t>https://www.tandfonline.com/journals/uwjo</t>
+  </si>
+  <si>
+    <t>2376-0605</t>
+  </si>
+  <si>
+    <t>AACE Clinical Case Reports</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/23760605</t>
+  </si>
+  <si>
+    <t>2590-0544</t>
+  </si>
+  <si>
+    <t>Chaos, Solitons &amp; Fractals: X</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/25900544</t>
+  </si>
+  <si>
+    <t>2212-9685</t>
+  </si>
+  <si>
+    <t>EuPA Open Proteomics</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/22129685</t>
+  </si>
+  <si>
+    <t>2307-4108</t>
+  </si>
+  <si>
+    <t>Kuwait Journal of Science</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/23074108</t>
+  </si>
+  <si>
+    <t>3050-8037</t>
+  </si>
+  <si>
+    <t>Global Economics Research</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30508037</t>
+  </si>
+  <si>
+    <t>3050-5798</t>
+  </si>
+  <si>
+    <t>Research in Neurodiversity</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30505798</t>
+  </si>
+  <si>
+    <t>3050-581X</t>
+  </si>
+  <si>
+    <t>Total Chemistry</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/3050581X</t>
+  </si>
+  <si>
+    <t>3050-8606</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence for Transportation</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30508606</t>
+  </si>
+  <si>
+    <t>3050-8592</t>
+  </si>
+  <si>
+    <t>Advancing Medical-Surgical Nursing</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30508592</t>
+  </si>
+  <si>
+    <t>1879-8500</t>
+  </si>
+  <si>
+    <t>Practical Radiation Oncology</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/18798500</t>
+  </si>
+  <si>
+    <t>3050-8355</t>
+  </si>
+  <si>
+    <t>Cleaner Food Systems</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30508355</t>
+  </si>
+  <si>
+    <t>3050-6212</t>
+  </si>
+  <si>
+    <t>Sustainable Chemistry for Biodiversity</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506212</t>
+  </si>
+  <si>
+    <t>3050-6611</t>
+  </si>
+  <si>
+    <t>Journal of Cardiac Failure - Intersections</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30506611</t>
+  </si>
+  <si>
+    <t>3050-9157</t>
+  </si>
+  <si>
+    <t>AACE Endocrinology and Diabetes</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30509157</t>
+  </si>
+  <si>
+    <t>3050-9890</t>
+  </si>
+  <si>
+    <t>Environmental Nexus</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30509890</t>
+  </si>
+  <si>
+    <t>0003-9098</t>
+  </si>
+  <si>
+    <t>European Poultry Science</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/00039098</t>
+  </si>
+  <si>
+    <t>3050-8401</t>
+  </si>
+  <si>
+    <t>Equity Neuroscience</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30508401</t>
+  </si>
+  <si>
+    <t>3050-5143</t>
+  </si>
+  <si>
+    <t>The Lancet Primary Care</t>
+  </si>
+  <si>
+    <t>http://www.sciencedirect.com/science/journal/30505143</t>
   </si>
 </sst>
 </file>
@@ -23492,6 +23655,456 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D09B647D-DD37-4427-854F-BF8FF8300300}">
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2827</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2828</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2829</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2830</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2831</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2832</v>
+      </c>
+      <c r="F3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2833</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2834</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2835</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2836</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2838</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2839</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2840</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2841</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2842</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2843</v>
+      </c>
+      <c r="E7" t="s">
+        <v>2844</v>
+      </c>
+      <c r="F7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2845</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2846</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2847</v>
+      </c>
+      <c r="F8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2848</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2849</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2850</v>
+      </c>
+      <c r="F9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2851</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2852</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2853</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B11" t="s">
+        <v>2854</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2855</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2856</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2857</v>
+      </c>
+      <c r="D12" t="s">
+        <v>2858</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2859</v>
+      </c>
+      <c r="F12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2860</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2861</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2862</v>
+      </c>
+      <c r="F13" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2863</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2864</v>
+      </c>
+      <c r="E14" t="s">
+        <v>2865</v>
+      </c>
+      <c r="F14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B15" t="s">
+        <v>2866</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E15" t="s">
+        <v>2868</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2869</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2870</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2871</v>
+      </c>
+      <c r="F16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B17" t="s">
+        <v>2872</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2873</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F17" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B18" t="s">
+        <v>2875</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2876</v>
+      </c>
+      <c r="E18" t="s">
+        <v>2877</v>
+      </c>
+      <c r="F18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B19" t="s">
+        <v>2878</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2879</v>
+      </c>
+      <c r="E19" t="s">
+        <v>2880</v>
+      </c>
+      <c r="F19" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0BCCC-3CC4-4163-A79C-06EC3FA0BA03}">
   <dimension ref="A1:H26"/>

--- a/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D8A57F6-CAEB-4491-843D-E6B5C0F691F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445176F8-72FE-4C02-9844-FF6C006255FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="10" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="11" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan8" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Nr8_april2" sheetId="9" r:id="rId9"/>
     <sheet name="Nr9_april29" sheetId="10" r:id="rId10"/>
     <sheet name="Nr10_juni5" sheetId="11" r:id="rId11"/>
+    <sheet name="Nr11_Juli2" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6453" uniqueCount="2881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6499" uniqueCount="2899">
   <si>
     <t>Imprint</t>
   </si>
@@ -8689,6 +8690,60 @@
   </si>
   <si>
     <t>http://www.sciencedirect.com/science/journal/30505143</t>
+  </si>
+  <si>
+    <t>0346-7821</t>
+  </si>
+  <si>
+    <t>Arbete och Hälsa</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/aoh</t>
+  </si>
+  <si>
+    <t>2004-108X</t>
+  </si>
+  <si>
+    <t>1100-5629</t>
+  </si>
+  <si>
+    <t>ASLA:s skriftserier = ASLA Studies in Applied Linguistics</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/asla</t>
+  </si>
+  <si>
+    <t>2003-3605</t>
+  </si>
+  <si>
+    <t>Journal of Praxis in Higher Education</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/jphe</t>
+  </si>
+  <si>
+    <t>2002-3871</t>
+  </si>
+  <si>
+    <t>0348-6133</t>
+  </si>
+  <si>
+    <t>Samlaren</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/samlaren</t>
+  </si>
+  <si>
+    <t>2003-5624</t>
+  </si>
+  <si>
+    <t>1104-1420 </t>
+  </si>
+  <si>
+    <t>Socialvetenskaplig tidskrift </t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/socvet</t>
   </si>
 </sst>
 </file>
@@ -24105,6 +24160,166 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64980D48-F239-425E-ACE4-C20AB0D27DCE}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2881</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2882</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2883</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2885</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2886</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2887</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2888</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2889</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2890</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2891</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2892</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2893</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2894</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2895</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2896</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2897</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0BCCC-3CC4-4163-A79C-06EC3FA0BA03}">
   <dimension ref="A1:H26"/>

--- a/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445176F8-72FE-4C02-9844-FF6C006255FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353FF70F-24C7-4EE9-B7CD-84BCBD6B7579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="11" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" firstSheet="2" activeTab="12" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan8" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,8 @@
     <sheet name="Nr8_april2" sheetId="9" r:id="rId9"/>
     <sheet name="Nr9_april29" sheetId="10" r:id="rId10"/>
     <sheet name="Nr10_juni5" sheetId="11" r:id="rId11"/>
-    <sheet name="Nr11_Juli2" sheetId="12" r:id="rId12"/>
+    <sheet name="Nr11_juli2" sheetId="12" r:id="rId12"/>
+    <sheet name="Nr12" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6499" uniqueCount="2899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6546" uniqueCount="2918">
   <si>
     <t>Imprint</t>
   </si>
@@ -8744,6 +8745,63 @@
   </si>
   <si>
     <t>https://publicera.kb.se/socvet</t>
+  </si>
+  <si>
+    <t>1474-0532</t>
+  </si>
+  <si>
+    <t>0263-6751</t>
+  </si>
+  <si>
+    <t>Anglo-Saxon England</t>
+  </si>
+  <si>
+    <t>http://www.cambridge.org/core/product/identifier/ASE/type/JOURNAL</t>
+  </si>
+  <si>
+    <t>2045-239X</t>
+  </si>
+  <si>
+    <t>0068-2462</t>
+  </si>
+  <si>
+    <t>Papers of the British School at Rome</t>
+  </si>
+  <si>
+    <t>https://www.cambridge.org/core/journals/papers-of-the-british-school-at-rome</t>
+  </si>
+  <si>
+    <t>2304-3857</t>
+  </si>
+  <si>
+    <t>0740-1558</t>
+  </si>
+  <si>
+    <t>Yearbook for Traditional Music</t>
+  </si>
+  <si>
+    <t>http://www.cambridge.org/core/product/identifier/YTM/type/JOURNAL</t>
+  </si>
+  <si>
+    <t>3049-5822</t>
+  </si>
+  <si>
+    <t>Advances in Psychological Science Open</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/PSO</t>
+  </si>
+  <si>
+    <t>1547-3325</t>
+  </si>
+  <si>
+    <t>1040-1237</t>
+  </si>
+  <si>
+    <t>Annals of Clinical Psychiatry</t>
+  </si>
+  <si>
+    <t>https://journals.sagepub.com/loi/ACY</t>
   </si>
 </sst>
 </file>
@@ -24320,6 +24378,169 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FC0088A-1BE3-4E72-A29C-84D4FA9234E8}">
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2899</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2900</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E2" t="s">
+        <v>2902</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2904</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2907</v>
+      </c>
+      <c r="C4" t="s">
+        <v>2908</v>
+      </c>
+      <c r="D4" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E4" t="s">
+        <v>2910</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2911</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E5" t="s">
+        <v>2913</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2914</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2915</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2916</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2917</v>
+      </c>
+      <c r="F6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0BCCC-3CC4-4163-A79C-06EC3FA0BA03}">
   <dimension ref="A1:H26"/>

--- a/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
+++ b/Bibsam_tidskriftslistor/Uppdateringar/tidskriftslistor_ändringar_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\Uppdateringar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{278382C2-3EE3-4ACE-821F-9D0B4AA23CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{550AB515-21A9-4162-9D4D-9837CB02BCA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" firstSheet="2" activeTab="12" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" firstSheet="3" activeTab="13" xr2:uid="{86D68454-0DC7-4E8F-AFCE-283EDE566798}"/>
   </bookViews>
   <sheets>
     <sheet name="Nr1_Jan8" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="Nr10_juni5" sheetId="11" r:id="rId11"/>
     <sheet name="Nr11_juli2" sheetId="12" r:id="rId12"/>
     <sheet name="Nr12_okt6" sheetId="13" r:id="rId13"/>
+    <sheet name="Nr13_okt8" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9691" uniqueCount="4269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9721" uniqueCount="4274">
   <si>
     <t>Imprint</t>
   </si>
@@ -12855,6 +12856,21 @@
   </si>
   <si>
     <t>https://link.springer.com/journal/13567</t>
+  </si>
+  <si>
+    <t>3035-6903</t>
+  </si>
+  <si>
+    <t>Current Issues in Work-Integrated Learning</t>
+  </si>
+  <si>
+    <t>https://publicera.kb.se/ciwil</t>
+  </si>
+  <si>
+    <t>ASLA:s skriftserie = ASLA Studies in Applied Linguistics</t>
+  </si>
+  <si>
+    <t>Rättning av titel</t>
   </si>
 </sst>
 </file>
@@ -38924,6 +38940,114 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0AA26DA-7DB1-411C-B140-C4AF1BBFCF43}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4269</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4270</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4271</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2885</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4272</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2887</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B4" t="s">
+        <v>454</v>
+      </c>
+      <c r="D4" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1962</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDE0BCCC-3CC4-4163-A79C-06EC3FA0BA03}">
   <dimension ref="A1:H26"/>
